--- a/program.xlsx
+++ b/program.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/matteo_francia2_studio_unibo_it/Documents/teaching-bigdata/AA2526-unibo-mldm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69C0621B-3DAF-4BAE-BB9C-873FC485E9EA}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8D3CADD-00B2-4C2C-B287-B1128E371365}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AA2526" sheetId="1" r:id="rId1"/>
+    <sheet name="AA2526 (2)" sheetId="2" r:id="rId1"/>
+    <sheet name="AA2526" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="34">
   <si>
     <t>Data preprocessing</t>
   </si>
@@ -60,12 +64,6 @@
     <t>Modeling</t>
   </si>
   <si>
-    <t>Ready</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>Data preprocessing (until data integration)</t>
   </si>
   <si>
@@ -87,9 +85,6 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>Topics</t>
-  </si>
-  <si>
     <t>Tot</t>
   </si>
   <si>
@@ -111,26 +106,47 @@
     <t>Fairness + Summing up</t>
   </si>
   <si>
-    <t>Missing</t>
-  </si>
-  <si>
     <t>Intro + CRISP-DM</t>
   </si>
   <si>
-    <t xml:space="preserve"> + Lab 00</t>
-  </si>
-  <si>
     <t>Business Understanding</t>
   </si>
   <si>
     <t xml:space="preserve"> + Data understanding</t>
+  </si>
+  <si>
+    <t>Lectures (in Class)</t>
+  </si>
+  <si>
+    <t>at home</t>
+  </si>
+  <si>
+    <t>Lab 00</t>
+  </si>
+  <si>
+    <t>CS: Sport</t>
+  </si>
+  <si>
+    <t>Lab: Understanding</t>
+  </si>
+  <si>
+    <t>Lab: Housing (Data Understanding)</t>
+  </si>
+  <si>
+    <t>Lab: Introduction to Colab</t>
+  </si>
+  <si>
+    <t>Follow-up at home</t>
+  </si>
+  <si>
+    <t>Data Understanding</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +158,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -179,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -218,6 +241,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,466 +533,859 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1BA7BF-4F83-4B95-BD26-B9FD6BCF8777}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5703125" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
-        <v>45559</v>
+        <v>45924</v>
       </c>
       <c r="B2" s="5">
         <f>WEEKDAY(A2)-1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="7">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4">
-        <f>SUM($F$2:F2)/$F$17</f>
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="7">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <f>SUM($G$2:G2)/$G$17</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <f>A2+7</f>
-        <v>45566</v>
+        <v>45931</v>
       </c>
       <c r="B3" s="5">
         <f t="shared" ref="B3:B15" si="0">WEEKDAY(A3)-1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="7">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <f>SUM($F$2:F3)/$F$17</f>
+      <c r="G3" s="7">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <f>SUM($G$2:G3)/$G$17</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <f t="shared" ref="A4:A15" si="1">A3+7</f>
-        <v>45573</v>
+        <v>45938</v>
       </c>
       <c r="B4" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="7">
-        <v>2</v>
-      </c>
-      <c r="G4" s="4">
-        <f>SUM($F$2:F4)/$F$17</f>
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="7">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4">
+        <f>SUM($G$2:G4)/$G$17</f>
         <v>0.25</v>
       </c>
-      <c r="H4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <f t="shared" si="1"/>
+        <v>45945</v>
+      </c>
+      <c r="B5" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4">
+        <f>SUM($G$2:G5)/$G$17</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <f t="shared" si="1"/>
+        <v>45952</v>
+      </c>
+      <c r="B6" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4">
+        <f>SUM($G$2:G6)/$G$17</f>
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <f t="shared" si="1"/>
+        <v>45959</v>
+      </c>
+      <c r="B7" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4">
+        <f>SUM($G$2:G7)/$G$17</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" si="1"/>
+        <v>45966</v>
+      </c>
+      <c r="B8" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
-        <f t="shared" si="1"/>
-        <v>45580</v>
-      </c>
-      <c r="B5" s="5">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="7">
-        <v>2</v>
-      </c>
-      <c r="G5" s="4">
-        <f>SUM($F$2:F5)/$F$17</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <f t="shared" si="1"/>
-        <v>45587</v>
-      </c>
-      <c r="B6" s="5">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4">
-        <f>SUM($F$2:F6)/$F$17</f>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <f t="shared" si="1"/>
-        <v>45594</v>
-      </c>
-      <c r="B7" s="5">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="4">
-        <f>SUM($F$2:F7)/$F$17</f>
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <f t="shared" si="1"/>
-        <v>45601</v>
-      </c>
-      <c r="B8" s="5">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="4">
-        <f>SUM($F$2:F8)/$F$17</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G8" s="7">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4">
+        <f>SUM($G$2:G8)/$G$17</f>
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <f t="shared" si="1"/>
-        <v>45608</v>
+        <v>45973</v>
       </c>
       <c r="B9" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="7">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4">
-        <f>SUM($F$2:F9)/$F$17</f>
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4">
+        <f>SUM($G$2:G9)/$G$17</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <f t="shared" si="1"/>
-        <v>45615</v>
+        <v>45980</v>
       </c>
       <c r="B10" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="7">
-        <v>2</v>
-      </c>
-      <c r="G10" s="4">
-        <f>SUM($F$2:F10)/$F$17</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="H10" s="4">
+        <f>SUM($G$2:G10)/$G$17</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <f t="shared" si="1"/>
-        <v>45622</v>
+        <v>45987</v>
       </c>
       <c r="B11" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="7">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4">
-        <f>SUM($F$2:F11)/$F$17</f>
-        <v>0.75</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="7">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4">
+        <f>SUM($G$2:G11)/$G$17</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <f t="shared" si="1"/>
-        <v>45629</v>
+        <v>45994</v>
       </c>
       <c r="B12" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="7">
-        <v>2</v>
-      </c>
-      <c r="G12" s="4">
-        <f>SUM($F$2:F12)/$F$17</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4">
+        <f>SUM($G$2:G12)/$G$17</f>
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <f>A12+7</f>
-        <v>45636</v>
+        <v>46001</v>
       </c>
       <c r="B13" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="7">
-        <v>2</v>
-      </c>
-      <c r="G13" s="4">
-        <f>SUM($F$2:F13)/$F$17</f>
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="H13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4">
+        <f>SUM($G$2:G13)/$G$17</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="B14" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
-        <f t="shared" si="1"/>
-        <v>45643</v>
-      </c>
-      <c r="B14" s="5">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="7">
-        <v>2</v>
-      </c>
-      <c r="G14" s="4">
-        <f>SUM($F$2:F14)/$F$17</f>
+      <c r="H14" s="4">
+        <f>SUM($G$2:G14)/$G$17</f>
         <v>1</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <f t="shared" si="1"/>
-        <v>45650</v>
+        <v>46015</v>
       </c>
       <c r="B15" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="5"/>
-      <c r="F15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="4">
-        <f>SUM($F$2:F15)/$F$17</f>
+      <c r="G15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="4">
+        <f>SUM($G$2:G15)/$G$17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="6"/>
       <c r="C16" s="13"/>
       <c r="D16" s="6"/>
       <c r="E16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="5">
+        <f>SUM(G2:G14)</f>
+        <v>24</v>
+      </c>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="E17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="1">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:A15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>45559</v>
+      </c>
+      <c r="B2" s="5">
+        <f>WEEKDAY(A2)-1</f>
+        <v>2</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="7">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <f>SUM($G$2:G2)/$G$17</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <f>A2+7</f>
+        <v>45566</v>
+      </c>
+      <c r="B3" s="5">
+        <f t="shared" ref="B3:B15" si="0">WEEKDAY(A3)-1</f>
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="7">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <f>SUM($G$2:G3)/$G$17</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <f t="shared" ref="A4:A15" si="1">A3+7</f>
+        <v>45573</v>
+      </c>
+      <c r="B4" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="7">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4">
+        <f>SUM($G$2:G4)/$G$17</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <f t="shared" si="1"/>
+        <v>45580</v>
+      </c>
+      <c r="B5" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4">
+        <f>SUM($G$2:G5)/$G$17</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <f t="shared" si="1"/>
+        <v>45587</v>
+      </c>
+      <c r="B6" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4">
+        <f>SUM($G$2:G6)/$G$17</f>
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <f t="shared" si="1"/>
+        <v>45594</v>
+      </c>
+      <c r="B7" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4">
+        <f>SUM($G$2:G7)/$G$17</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" si="1"/>
+        <v>45601</v>
+      </c>
+      <c r="B8" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="4">
+        <f>SUM($G$2:G8)/$G$17</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="1"/>
+        <v>45608</v>
+      </c>
+      <c r="B9" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4">
+        <f>SUM($G$2:G9)/$G$17</f>
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="1"/>
+        <v>45615</v>
+      </c>
+      <c r="B10" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="H10" s="4">
+        <f>SUM($G$2:G10)/$G$17</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="1"/>
+        <v>45622</v>
+      </c>
+      <c r="B11" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="5">
-        <f>SUM(F2:F14)</f>
+      <c r="G11" s="7">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4">
+        <f>SUM($G$2:G11)/$G$17</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="1"/>
+        <v>45629</v>
+      </c>
+      <c r="B12" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4">
+        <f>SUM($G$2:G12)/$G$17</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f>A12+7</f>
+        <v>45636</v>
+      </c>
+      <c r="B13" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4">
+        <f>SUM($G$2:G13)/$G$17</f>
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="1"/>
+        <v>45643</v>
+      </c>
+      <c r="B14" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="7">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4">
+        <f>SUM($G$2:G14)/$G$17</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="1"/>
+        <v>45650</v>
+      </c>
+      <c r="B15" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="5"/>
+      <c r="G15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="4">
+        <f>SUM($G$2:G15)/$G$17</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="5">
+        <f>SUM(G2:G14)</f>
         <v>24</v>
       </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="1">
+        <v>16</v>
+      </c>
+      <c r="G17" s="1">
         <v>24</v>
       </c>
     </row>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/matteo_francia2_studio_unibo_it/Documents/teaching-bigdata/AA2526-unibo-mldm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8D3CADD-00B2-4C2C-B287-B1128E371365}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5946CC44-D23D-4090-930F-2879DE428C11}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AA2526 (2)" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="36">
   <si>
     <t>Data preprocessing</t>
   </si>
@@ -140,13 +140,19 @@
   </si>
   <si>
     <t>Data Understanding</t>
+  </si>
+  <si>
+    <t>Data preprocessing (until data normalization)</t>
+  </si>
+  <si>
+    <t>Lab: Preprocessing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +164,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -242,14 +254,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -535,20 +545,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1BA7BF-4F83-4B95-BD26-B9FD6BCF8777}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.5703125" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="4.26953125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.54296875" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -575,7 +585,7 @@
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <v>45924</v>
       </c>
@@ -603,7 +613,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <f>A2+7</f>
         <v>45931</v>
@@ -632,7 +642,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <f t="shared" ref="A4:A15" si="1">A3+7</f>
         <v>45938</v>
@@ -661,7 +671,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <f t="shared" si="1"/>
         <v>45945</v>
@@ -676,7 +686,7 @@
       <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="7">
@@ -687,7 +697,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <f t="shared" si="1"/>
         <v>45952</v>
@@ -699,9 +709,11 @@
       <c r="C6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="15" t="s">
-        <v>0</v>
+      <c r="D6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="G6" s="7">
         <v>2</v>
@@ -711,7 +723,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <f t="shared" si="1"/>
         <v>45959</v>
@@ -723,9 +735,14 @@
       <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="E7" s="15" t="s">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
       </c>
       <c r="G7" s="7">
         <v>2</v>
@@ -735,7 +752,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <f t="shared" si="1"/>
         <v>45966</v>
@@ -747,9 +764,11 @@
       <c r="C8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="E8" s="15" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G8" s="7">
         <v>2</v>
@@ -759,7 +778,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <f t="shared" si="1"/>
         <v>45973</v>
@@ -771,9 +790,9 @@
       <c r="C9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="15" t="s">
-        <v>4</v>
+      <c r="D9" s="16"/>
+      <c r="E9" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="G9" s="7">
         <v>2</v>
@@ -783,7 +802,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <f t="shared" si="1"/>
         <v>45980</v>
@@ -795,9 +814,9 @@
       <c r="C10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="15" t="s">
-        <v>7</v>
+      <c r="D10" s="16"/>
+      <c r="E10" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="G10" s="7">
         <v>2</v>
@@ -807,7 +826,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <f t="shared" si="1"/>
         <v>45987</v>
@@ -819,9 +838,9 @@
       <c r="C11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="15" t="s">
-        <v>18</v>
+      <c r="D11" s="16"/>
+      <c r="E11" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="G11" s="7">
         <v>2</v>
@@ -831,7 +850,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <f t="shared" si="1"/>
         <v>45994</v>
@@ -843,9 +862,9 @@
       <c r="C12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="15" t="s">
-        <v>17</v>
+      <c r="D12" s="16"/>
+      <c r="E12" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="G12" s="7">
         <v>2</v>
@@ -855,7 +874,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <f>A12+7</f>
         <v>46001</v>
@@ -867,10 +886,7 @@
       <c r="C13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="15" t="s">
-        <v>19</v>
-      </c>
+      <c r="D13" s="16"/>
       <c r="G13" s="7">
         <v>2</v>
       </c>
@@ -879,7 +895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <f t="shared" si="1"/>
         <v>46008</v>
@@ -891,10 +907,7 @@
       <c r="C14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="15" t="s">
-        <v>21</v>
-      </c>
+      <c r="D14" s="16"/>
       <c r="G14" s="7" t="s">
         <v>9</v>
       </c>
@@ -903,7 +916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <f t="shared" si="1"/>
         <v>46015</v>
@@ -914,6 +927,9 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="5"/>
+      <c r="E15" s="15" t="s">
+        <v>21</v>
+      </c>
       <c r="G15" s="5" t="s">
         <v>9</v>
       </c>
@@ -922,7 +938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="6"/>
       <c r="C16" s="13"/>
@@ -936,7 +952,7 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E17" s="9" t="s">
         <v>16</v>
       </c>
@@ -965,20 +981,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="4.26953125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1005,7 +1021,7 @@
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <v>45559</v>
       </c>
@@ -1033,7 +1049,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <f>A2+7</f>
         <v>45566</v>
@@ -1062,7 +1078,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <f t="shared" ref="A4:A15" si="1">A3+7</f>
         <v>45573</v>
@@ -1077,7 +1093,7 @@
       <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="7">
@@ -1088,7 +1104,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <f t="shared" si="1"/>
         <v>45580</v>
@@ -1103,7 +1119,7 @@
       <c r="D5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="7">
@@ -1114,7 +1130,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <f t="shared" si="1"/>
         <v>45587</v>
@@ -1129,7 +1145,7 @@
       <c r="D6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="7">
@@ -1140,7 +1156,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <f t="shared" si="1"/>
         <v>45594</v>
@@ -1155,7 +1171,7 @@
       <c r="D7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="7">
@@ -1166,7 +1182,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <f t="shared" si="1"/>
         <v>45601</v>
@@ -1181,7 +1197,7 @@
       <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="7" t="s">
@@ -1192,7 +1208,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <f t="shared" si="1"/>
         <v>45608</v>
@@ -1207,7 +1223,7 @@
       <c r="D9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="7">
@@ -1218,7 +1234,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <f t="shared" si="1"/>
         <v>45615</v>
@@ -1233,7 +1249,7 @@
       <c r="D10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="7">
@@ -1244,7 +1260,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <f t="shared" si="1"/>
         <v>45622</v>
@@ -1259,7 +1275,7 @@
       <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>18</v>
       </c>
       <c r="G11" s="7">
@@ -1270,7 +1286,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <f t="shared" si="1"/>
         <v>45629</v>
@@ -1285,7 +1301,7 @@
       <c r="D12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="7">
@@ -1296,7 +1312,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <f>A12+7</f>
         <v>45636</v>
@@ -1311,7 +1327,7 @@
       <c r="D13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="7">
@@ -1322,7 +1338,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <f t="shared" si="1"/>
         <v>45643</v>
@@ -1337,7 +1353,7 @@
       <c r="D14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>21</v>
       </c>
       <c r="G14" s="7">
@@ -1348,7 +1364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <f t="shared" si="1"/>
         <v>45650</v>
@@ -1367,7 +1383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="6"/>
       <c r="C16" s="13"/>
@@ -1381,7 +1397,7 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E17" s="9" t="s">
         <v>16</v>
       </c>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/matteo_francia2_studio_unibo_it/Documents/teaching-bigdata/AA2526-unibo-mldm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5946CC44-D23D-4090-930F-2879DE428C11}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA3D6B5-3B3F-4620-B579-492523FB4C5D}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AA2526 (2)" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="36">
   <si>
     <t>Data preprocessing</t>
   </si>
@@ -790,8 +790,10 @@
       <c r="C9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="18" t="s">
+      <c r="D9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="7">

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/matteo_francia2_studio_unibo_it/Documents/teaching-bigdata/AA2526-unibo-mldm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA3D6B5-3B3F-4620-B579-492523FB4C5D}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DCC497-A1D8-454A-B4FE-BC5693B603E6}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="37">
   <si>
     <t>Data preprocessing</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>Lab: Preprocessing</t>
+  </si>
+  <si>
+    <t>Modeling (until k-nn)</t>
   </si>
 </sst>
 </file>
@@ -794,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G9" s="7">
         <v>2</v>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/matteo_francia2_studio_unibo_it/Documents/teaching-bigdata/AA2526-unibo-mldm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DCC497-A1D8-454A-B4FE-BC5693B603E6}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC45E72-80B4-4FC8-B262-DBDD416AAA2A}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AA2526 (2)" sheetId="2" r:id="rId1"/>
-    <sheet name="AA2526" sheetId="1" r:id="rId2"/>
+    <sheet name="AA2425" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="40">
   <si>
     <t>Data preprocessing</t>
   </si>
@@ -149,13 +149,22 @@
   </si>
   <si>
     <t>Modeling (until k-nn)</t>
+  </si>
+  <si>
+    <t>AutoML + Fairness</t>
+  </si>
+  <si>
+    <t>Data preprocessing, Lab: Housing</t>
+  </si>
+  <si>
+    <t>Modeling, Lab: Housing (until AutoML)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,7 +188,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -214,10 +230,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -262,10 +279,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Percentuale" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -550,13 +571,13 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.26953125" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="14" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.54296875" customWidth="1"/>
+    <col min="5" max="5" width="39.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -611,7 +632,7 @@
       <c r="G2" s="7">
         <v>2</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="18">
         <f>SUM($G$2:G2)/$G$17</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -640,7 +661,7 @@
       <c r="G3" s="7">
         <v>2</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="18">
         <f>SUM($G$2:G3)/$G$17</f>
         <v>0.16666666666666666</v>
       </c>
@@ -669,7 +690,7 @@
       <c r="G4" s="7">
         <v>2</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="18">
         <f>SUM($G$2:G4)/$G$17</f>
         <v>0.25</v>
       </c>
@@ -695,7 +716,7 @@
       <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="18">
         <f>SUM($G$2:G5)/$G$17</f>
         <v>0.33333333333333331</v>
       </c>
@@ -721,7 +742,7 @@
       <c r="G6" s="7">
         <v>2</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="18">
         <f>SUM($G$2:G6)/$G$17</f>
         <v>0.41666666666666669</v>
       </c>
@@ -742,7 +763,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
         <v>35</v>
@@ -750,7 +771,7 @@
       <c r="G7" s="7">
         <v>2</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="18">
         <f>SUM($G$2:G7)/$G$17</f>
         <v>0.5</v>
       </c>
@@ -776,7 +797,7 @@
       <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="18">
         <f>SUM($G$2:G8)/$G$17</f>
         <v>0.58333333333333337</v>
       </c>
@@ -793,8 +814,8 @@
       <c r="C9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>11</v>
+      <c r="D9" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>36</v>
@@ -802,7 +823,7 @@
       <c r="G9" s="7">
         <v>2</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="18">
         <f>SUM($G$2:G9)/$G$17</f>
         <v>0.66666666666666663</v>
       </c>
@@ -819,14 +840,16 @@
       <c r="C10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="18" t="s">
-        <v>18</v>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="G10" s="7">
         <v>2</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="18">
         <f>SUM($G$2:G10)/$G$17</f>
         <v>0.75</v>
       </c>
@@ -843,14 +866,16 @@
       <c r="C11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="18" t="s">
-        <v>17</v>
+      <c r="D11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="7">
         <v>2</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="18">
         <f>SUM($G$2:G11)/$G$17</f>
         <v>0.83333333333333337</v>
       </c>
@@ -867,14 +892,16 @@
       <c r="C12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="18" t="s">
-        <v>19</v>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="G12" s="7">
         <v>2</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="18">
         <f>SUM($G$2:G12)/$G$17</f>
         <v>0.91666666666666663</v>
       </c>
@@ -891,16 +918,21 @@
       <c r="C13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="G13" s="7">
         <v>2</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="18">
         <f>SUM($G$2:G13)/$G$17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <f t="shared" si="1"/>
         <v>46008</v>
@@ -943,7 +975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="6"/>
       <c r="C16" s="13"/>
@@ -957,7 +989,7 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="E17" s="9" t="s">
         <v>16</v>
       </c>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/matteo_francia2_studio_unibo_it/Documents/teaching-bigdata/AA2526-unibo-mldm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC45E72-80B4-4FC8-B262-DBDD416AAA2A}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="11_F25DC773A252ABDACC10480B991D78805BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{008EF8F6-9F71-4F2A-8B12-D734D1DE2C08}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="15990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AA2526 (2)" sheetId="2" r:id="rId1"/>
+    <sheet name="AA2526" sheetId="2" r:id="rId1"/>
     <sheet name="AA2425" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,126 +38,129 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="41">
+  <si>
+    <t>When</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>What</t>
+  </si>
+  <si>
+    <t>Lectures (in Class)</t>
+  </si>
+  <si>
+    <t>Follow-up at home</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Coverage</t>
+  </si>
+  <si>
+    <t>Lab 4.2 (13-15)</t>
+  </si>
+  <si>
+    <t>Theory</t>
+  </si>
+  <si>
+    <t>Intro + CRISP-DM</t>
+  </si>
+  <si>
+    <t>Lab: Introduction to Colab</t>
+  </si>
+  <si>
+    <t>Business Understanding</t>
+  </si>
+  <si>
+    <t>CS: Sport</t>
+  </si>
+  <si>
+    <t>Data Understanding</t>
+  </si>
+  <si>
+    <t>Lab: Understanding</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t>Lab: Housing (Data Understanding)</t>
+  </si>
+  <si>
+    <t>Data preprocessing (until data normalization)</t>
+  </si>
+  <si>
+    <t>Data preprocessing, Lab: Housing</t>
+  </si>
+  <si>
+    <t>Lab: Preprocessing</t>
+  </si>
+  <si>
+    <t>(Deep) neural networks</t>
+  </si>
+  <si>
+    <t>Modeling (until k-nn)</t>
+  </si>
+  <si>
+    <t>Modeling, Lab: Housing (until AutoML)</t>
+  </si>
+  <si>
+    <t>AutoML + Fairness</t>
+  </si>
+  <si>
+    <t>Lab: Challenge</t>
+  </si>
+  <si>
+    <t>Lab: Challenge Solution + Peer Review</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Fairness + Summing up</t>
+  </si>
+  <si>
+    <t>Tot</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>at home</t>
+  </si>
+  <si>
+    <t>Lab 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + Data understanding</t>
+  </si>
+  <si>
+    <t>Lab: Data understanding + Housing</t>
+  </si>
+  <si>
+    <t>Data preprocessing (until data integration)</t>
+  </si>
   <si>
     <t>Data preprocessing</t>
   </si>
   <si>
-    <t>What</t>
-  </si>
-  <si>
-    <t>When</t>
-  </si>
-  <si>
-    <t>Coverage</t>
-  </si>
-  <si>
-    <t>(Deep) neural networks</t>
-  </si>
-  <si>
-    <t>Lab: Data understanding + Housing</t>
-  </si>
-  <si>
     <t>Lab: Data Preparation + Housing</t>
   </si>
   <si>
     <t>Modeling</t>
   </si>
   <si>
-    <t>Data preprocessing (until data integration)</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Theory</t>
-  </si>
-  <si>
-    <t>Lab</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>Tot</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Lab: Challenge</t>
-  </si>
-  <si>
     <t>Lab: Housing + Titanic</t>
   </si>
   <si>
     <t>Lab: Challenge Solution + AutoML</t>
-  </si>
-  <si>
-    <t>Lab 4.2 (13-15)</t>
-  </si>
-  <si>
-    <t>Fairness + Summing up</t>
-  </si>
-  <si>
-    <t>Intro + CRISP-DM</t>
-  </si>
-  <si>
-    <t>Business Understanding</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> + Data understanding</t>
-  </si>
-  <si>
-    <t>Lectures (in Class)</t>
-  </si>
-  <si>
-    <t>at home</t>
-  </si>
-  <si>
-    <t>Lab 00</t>
-  </si>
-  <si>
-    <t>CS: Sport</t>
-  </si>
-  <si>
-    <t>Lab: Understanding</t>
-  </si>
-  <si>
-    <t>Lab: Housing (Data Understanding)</t>
-  </si>
-  <si>
-    <t>Lab: Introduction to Colab</t>
-  </si>
-  <si>
-    <t>Follow-up at home</t>
-  </si>
-  <si>
-    <t>Data Understanding</t>
-  </si>
-  <si>
-    <t>Data preprocessing (until data normalization)</t>
-  </si>
-  <si>
-    <t>Lab: Preprocessing</t>
-  </si>
-  <si>
-    <t>Modeling (until k-nn)</t>
-  </si>
-  <si>
-    <t>AutoML + Fairness</t>
-  </si>
-  <si>
-    <t>Data preprocessing, Lab: Housing</t>
-  </si>
-  <si>
-    <t>Modeling, Lab: Housing (until AutoML)</t>
   </si>
 </sst>
 </file>
@@ -195,7 +198,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="2" tint="-0.249977111117893"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -234,7 +237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -274,10 +277,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -299,10 +298,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,40 +567,40 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.26953125" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="14" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="4.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="14" customWidth="1"/>
     <col min="4" max="4" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3"/>
     </row>
@@ -618,21 +613,21 @@
         <v>3</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
       <c r="G2" s="7">
         <v>2</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="16">
         <f>SUM($G$2:G2)/$G$17</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -647,21 +642,21 @@
         <v>3</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G3" s="7">
         <v>2</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="16">
         <f>SUM($G$2:G3)/$G$17</f>
         <v>0.16666666666666666</v>
       </c>
@@ -676,21 +671,21 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G4" s="7">
         <v>2</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="16">
         <f>SUM($G$2:G4)/$G$17</f>
         <v>0.25</v>
       </c>
@@ -705,18 +700,18 @@
         <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="16">
         <f>SUM($G$2:G5)/$G$17</f>
         <v>0.33333333333333331</v>
       </c>
@@ -731,18 +726,18 @@
         <v>3</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>34</v>
+        <v>9</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="G6" s="7">
         <v>2</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="16">
         <f>SUM($G$2:G6)/$G$17</f>
         <v>0.41666666666666669</v>
       </c>
@@ -757,21 +752,21 @@
         <v>3</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
       <c r="G7" s="7">
         <v>2</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="16">
         <f>SUM($G$2:G7)/$G$17</f>
         <v>0.5</v>
       </c>
@@ -786,18 +781,18 @@
         <v>3</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
       </c>
       <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="16">
         <f>SUM($G$2:G8)/$G$17</f>
         <v>0.58333333333333337</v>
       </c>
@@ -812,18 +807,18 @@
         <v>3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>36</v>
+        <v>16</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="G9" s="7">
         <v>2</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="16">
         <f>SUM($G$2:G9)/$G$17</f>
         <v>0.66666666666666663</v>
       </c>
@@ -838,18 +833,18 @@
         <v>3</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>39</v>
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
       </c>
       <c r="G10" s="7">
         <v>2</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="16">
         <f>SUM($G$2:G10)/$G$17</f>
         <v>0.75</v>
       </c>
@@ -864,18 +859,18 @@
         <v>3</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="G11" s="7">
         <v>2</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="16">
         <f>SUM($G$2:G11)/$G$17</f>
         <v>0.83333333333333337</v>
       </c>
@@ -890,18 +885,18 @@
         <v>3</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="G12" s="7">
         <v>2</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="16">
         <f>SUM($G$2:G12)/$G$17</f>
         <v>0.91666666666666663</v>
       </c>
@@ -916,23 +911,23 @@
         <v>3</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="G13" s="7">
         <v>2</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="16">
         <f>SUM($G$2:G13)/$G$17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <f t="shared" si="1"/>
         <v>46008</v>
@@ -942,46 +937,37 @@
         <v>3</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="D14" s="5"/>
       <c r="G14" s="7" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H14" s="4">
         <f>SUM($G$2:G14)/$G$17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="B15" s="5">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="12"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="10"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="G15" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H15" s="4">
         <f>SUM($G$2:G15)/$G$17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="6"/>
       <c r="C16" s="13"/>
       <c r="D16" s="6"/>
       <c r="E16" s="9" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G16" s="5">
         <f>SUM(G2:G14)</f>
@@ -989,9 +975,9 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="5:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E17" s="9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
@@ -1033,28 +1019,28 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3"/>
     </row>
@@ -1067,16 +1053,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G2" s="7">
         <v>2</v>
@@ -1096,16 +1082,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G3" s="7">
         <v>2</v>
@@ -1125,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
       </c>
       <c r="G4" s="7">
         <v>2</v>
@@ -1151,13 +1137,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -1177,13 +1163,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
       </c>
       <c r="G6" s="7">
         <v>2</v>
@@ -1203,13 +1189,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
       </c>
       <c r="G7" s="7">
         <v>2</v>
@@ -1229,16 +1215,16 @@
         <v>2</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>9</v>
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H8" s="4">
         <f>SUM($G$2:G8)/$G$17</f>
@@ -1255,13 +1241,13 @@
         <v>2</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
       </c>
       <c r="G9" s="7">
         <v>2</v>
@@ -1281,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
       </c>
       <c r="G10" s="7">
         <v>2</v>
@@ -1307,13 +1293,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
       </c>
       <c r="G11" s="7">
         <v>2</v>
@@ -1333,13 +1319,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
       </c>
       <c r="G12" s="7">
         <v>2</v>
@@ -1359,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
       </c>
       <c r="G13" s="7">
         <v>2</v>
@@ -1385,13 +1371,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
       </c>
       <c r="G14" s="7">
         <v>2</v>
@@ -1413,7 +1399,7 @@
       <c r="C15" s="10"/>
       <c r="D15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H15" s="4">
         <f>SUM($G$2:G15)/$G$17</f>
@@ -1426,7 +1412,7 @@
       <c r="C16" s="13"/>
       <c r="D16" s="6"/>
       <c r="E16" s="9" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G16" s="5">
         <f>SUM(G2:G14)</f>
@@ -1436,7 +1422,7 @@
     </row>
     <row r="17" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E17" s="9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
